--- a/数据表/NPC.xlsx
+++ b/数据表/NPC.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="56">
   <si>
     <t>//注释,npcid</t>
   </si>
@@ -172,64 +172,31 @@
     <t>刀盾兵</t>
   </si>
   <si>
-    <t>(Att,2),(Hp,10),(Speed,5)</t>
-  </si>
-  <si>
-    <t>(Vision,10)</t>
-  </si>
-  <si>
     <t>巨盾兵</t>
   </si>
   <si>
-    <t>(Att,2),(Hp,20),(Speed,5)</t>
-  </si>
-  <si>
     <t>短弓手</t>
   </si>
   <si>
-    <t>(Att,4),(Hp,5),(Speed,5)</t>
-  </si>
-  <si>
     <t>长弓手</t>
   </si>
   <si>
-    <t>(Att,5),(Hp,8),(Speed,5)</t>
-  </si>
-  <si>
     <t>轻骑兵</t>
   </si>
   <si>
-    <t>(Att,3),(Hp,7),(Speed,10)</t>
-  </si>
-  <si>
     <t>重骑兵</t>
   </si>
   <si>
-    <t>(Att,4),(Hp,10),(Speed,10)</t>
-  </si>
-  <si>
     <t>冲车</t>
   </si>
   <si>
-    <t>(Att,1),(Hp,20),(Speed,3)</t>
-  </si>
-  <si>
     <t>投石车</t>
   </si>
   <si>
-    <t>(Att,2),(Hp,30),(Speed,3)</t>
-  </si>
-  <si>
     <t>军医</t>
   </si>
   <si>
-    <t>(Att,1),(Hp,15),(Speed,5)</t>
-  </si>
-  <si>
     <t>巫医</t>
-  </si>
-  <si>
-    <t>(Att,2),(Hp,25),(Speed,5)</t>
   </si>
 </sst>
 </file>
@@ -845,12 +812,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1166,10 +1136,10 @@
   <dimension ref="A1:V62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="10.375" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="11.875" customWidth="1"/>
     <col min="3" max="3" width="12.375" customWidth="1"/>
-    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="5" max="5" width="17.25" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="12.125" customWidth="1"/>
@@ -1178,7 +1148,9 @@
     <col min="10" max="12" width="18.375" customWidth="1"/>
     <col min="13" max="13" width="26.75" customWidth="1"/>
     <col min="14" max="16" width="23.75" customWidth="1"/>
-    <col min="17" max="21" width="18.375" customWidth="1"/>
+    <col min="17" max="17" width="18.375" customWidth="1"/>
+    <col min="18" max="18" width="15.25" customWidth="1"/>
+    <col min="19" max="21" width="18.375" customWidth="1"/>
     <col min="22" max="22" width="13.5" customWidth="1"/>
     <col min="23" max="28" width="10.75" customWidth="1"/>
   </cols>
@@ -1351,10 +1323,10 @@
         <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O3" t="s">
         <v>43</v>
@@ -1415,17 +1387,20 @@
       <c r="L4">
         <v>2</v>
       </c>
-      <c r="M4" t="s">
-        <v>47</v>
-      </c>
-      <c r="N4" t="s">
-        <v>48</v>
+      <c r="M4" s="2">
+        <v>10000001</v>
+      </c>
+      <c r="N4">
+        <v>10010001</v>
       </c>
       <c r="O4">
         <v>1</v>
       </c>
       <c r="P4">
         <v>10</v>
+      </c>
+      <c r="Q4">
+        <v>1001</v>
       </c>
       <c r="S4">
         <v>2</v>
@@ -1471,17 +1446,20 @@
       <c r="L5">
         <v>2</v>
       </c>
-      <c r="M5" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5" t="s">
-        <v>48</v>
+      <c r="M5" s="2">
+        <v>10000002</v>
+      </c>
+      <c r="N5">
+        <v>10010002</v>
       </c>
       <c r="O5">
         <v>1</v>
       </c>
       <c r="P5">
         <v>10</v>
+      </c>
+      <c r="Q5">
+        <v>1001</v>
       </c>
       <c r="S5">
         <v>2</v>
@@ -1527,17 +1505,20 @@
       <c r="L6">
         <v>2</v>
       </c>
-      <c r="M6" t="s">
-        <v>47</v>
-      </c>
-      <c r="N6" t="s">
-        <v>48</v>
+      <c r="M6" s="2">
+        <v>10000003</v>
+      </c>
+      <c r="N6">
+        <v>10010003</v>
       </c>
       <c r="O6">
         <v>1</v>
       </c>
       <c r="P6">
         <v>10</v>
+      </c>
+      <c r="Q6">
+        <v>1001</v>
       </c>
       <c r="S6">
         <v>2</v>
@@ -1583,17 +1564,20 @@
       <c r="L7">
         <v>2</v>
       </c>
-      <c r="M7" t="s">
-        <v>47</v>
-      </c>
-      <c r="N7" t="s">
-        <v>48</v>
+      <c r="M7" s="2">
+        <v>10000004</v>
+      </c>
+      <c r="N7">
+        <v>10010004</v>
       </c>
       <c r="O7">
         <v>1</v>
       </c>
       <c r="P7">
         <v>10</v>
+      </c>
+      <c r="Q7">
+        <v>1001</v>
       </c>
       <c r="S7">
         <v>2</v>
@@ -1639,17 +1623,20 @@
       <c r="L8">
         <v>2</v>
       </c>
-      <c r="M8" t="s">
-        <v>47</v>
-      </c>
-      <c r="N8" t="s">
-        <v>48</v>
+      <c r="M8" s="2">
+        <v>10000005</v>
+      </c>
+      <c r="N8">
+        <v>10010005</v>
       </c>
       <c r="O8">
         <v>1</v>
       </c>
       <c r="P8">
         <v>10</v>
+      </c>
+      <c r="Q8">
+        <v>1001</v>
       </c>
       <c r="S8">
         <v>2</v>
@@ -1695,17 +1682,20 @@
       <c r="L9">
         <v>2</v>
       </c>
-      <c r="M9" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" t="s">
-        <v>48</v>
+      <c r="M9" s="2">
+        <v>10000006</v>
+      </c>
+      <c r="N9">
+        <v>10010006</v>
       </c>
       <c r="O9">
         <v>1</v>
       </c>
       <c r="P9">
         <v>10</v>
+      </c>
+      <c r="Q9">
+        <v>1001</v>
       </c>
       <c r="S9">
         <v>2</v>
@@ -1751,17 +1741,20 @@
       <c r="L10">
         <v>2</v>
       </c>
-      <c r="M10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" t="s">
-        <v>48</v>
+      <c r="M10" s="2">
+        <v>10000007</v>
+      </c>
+      <c r="N10">
+        <v>10010007</v>
       </c>
       <c r="O10">
         <v>1</v>
       </c>
       <c r="P10">
         <v>10</v>
+      </c>
+      <c r="Q10">
+        <v>1001</v>
       </c>
       <c r="S10">
         <v>2</v>
@@ -1807,17 +1800,20 @@
       <c r="L11">
         <v>2</v>
       </c>
-      <c r="M11" t="s">
-        <v>47</v>
-      </c>
-      <c r="N11" t="s">
-        <v>48</v>
+      <c r="M11" s="2">
+        <v>10000008</v>
+      </c>
+      <c r="N11">
+        <v>10010008</v>
       </c>
       <c r="O11">
         <v>1</v>
       </c>
       <c r="P11">
         <v>10</v>
+      </c>
+      <c r="Q11">
+        <v>1001</v>
       </c>
       <c r="S11">
         <v>2</v>
@@ -1863,17 +1859,20 @@
       <c r="L12">
         <v>2</v>
       </c>
-      <c r="M12" t="s">
-        <v>47</v>
-      </c>
-      <c r="N12" t="s">
-        <v>48</v>
+      <c r="M12" s="2">
+        <v>10000009</v>
+      </c>
+      <c r="N12">
+        <v>10010009</v>
       </c>
       <c r="O12">
         <v>1</v>
       </c>
       <c r="P12">
         <v>10</v>
+      </c>
+      <c r="Q12">
+        <v>1001</v>
       </c>
       <c r="S12">
         <v>2</v>
@@ -1919,17 +1918,20 @@
       <c r="L13">
         <v>2</v>
       </c>
-      <c r="M13" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" t="s">
-        <v>48</v>
+      <c r="M13" s="2">
+        <v>10000010</v>
+      </c>
+      <c r="N13">
+        <v>10010010</v>
       </c>
       <c r="O13">
         <v>1</v>
       </c>
       <c r="P13">
         <v>10</v>
+      </c>
+      <c r="Q13">
+        <v>1001</v>
       </c>
       <c r="S13">
         <v>2</v>
@@ -1975,17 +1977,20 @@
       <c r="L14">
         <v>2</v>
       </c>
-      <c r="M14" t="s">
-        <v>47</v>
-      </c>
-      <c r="N14" t="s">
-        <v>48</v>
+      <c r="M14" s="2">
+        <v>10000011</v>
+      </c>
+      <c r="N14">
+        <v>10010011</v>
       </c>
       <c r="O14">
         <v>1</v>
       </c>
       <c r="P14">
         <v>10</v>
+      </c>
+      <c r="Q14">
+        <v>1001</v>
       </c>
       <c r="S14">
         <v>2</v>
@@ -2031,17 +2036,20 @@
       <c r="L15">
         <v>2</v>
       </c>
-      <c r="M15" t="s">
-        <v>47</v>
-      </c>
-      <c r="N15" t="s">
-        <v>48</v>
+      <c r="M15" s="2">
+        <v>10000012</v>
+      </c>
+      <c r="N15">
+        <v>10010012</v>
       </c>
       <c r="O15">
         <v>1</v>
       </c>
       <c r="P15">
         <v>10</v>
+      </c>
+      <c r="Q15">
+        <v>1001</v>
       </c>
       <c r="S15">
         <v>2</v>
@@ -2087,17 +2095,20 @@
       <c r="L16">
         <v>2</v>
       </c>
-      <c r="M16" t="s">
-        <v>47</v>
-      </c>
-      <c r="N16" t="s">
-        <v>48</v>
+      <c r="M16" s="2">
+        <v>10000013</v>
+      </c>
+      <c r="N16">
+        <v>10010013</v>
       </c>
       <c r="O16">
         <v>1</v>
       </c>
       <c r="P16">
         <v>10</v>
+      </c>
+      <c r="Q16">
+        <v>1001</v>
       </c>
       <c r="S16">
         <v>2</v>
@@ -2143,17 +2154,20 @@
       <c r="L17">
         <v>2</v>
       </c>
-      <c r="M17" t="s">
-        <v>47</v>
-      </c>
-      <c r="N17" t="s">
-        <v>48</v>
+      <c r="M17" s="2">
+        <v>10000014</v>
+      </c>
+      <c r="N17">
+        <v>10010014</v>
       </c>
       <c r="O17">
         <v>1</v>
       </c>
       <c r="P17">
         <v>10</v>
+      </c>
+      <c r="Q17">
+        <v>1001</v>
       </c>
       <c r="S17">
         <v>2</v>
@@ -2199,17 +2213,20 @@
       <c r="L18">
         <v>2</v>
       </c>
-      <c r="M18" t="s">
-        <v>47</v>
-      </c>
-      <c r="N18" t="s">
-        <v>48</v>
+      <c r="M18" s="2">
+        <v>10000015</v>
+      </c>
+      <c r="N18">
+        <v>10010015</v>
       </c>
       <c r="O18">
         <v>1</v>
       </c>
       <c r="P18">
         <v>10</v>
+      </c>
+      <c r="Q18">
+        <v>1001</v>
       </c>
       <c r="S18">
         <v>2</v>
@@ -2255,17 +2272,20 @@
       <c r="L19">
         <v>2</v>
       </c>
-      <c r="M19" t="s">
-        <v>47</v>
-      </c>
-      <c r="N19" t="s">
-        <v>48</v>
+      <c r="M19" s="2">
+        <v>10000016</v>
+      </c>
+      <c r="N19">
+        <v>10010016</v>
       </c>
       <c r="O19">
         <v>1</v>
       </c>
       <c r="P19">
         <v>10</v>
+      </c>
+      <c r="Q19">
+        <v>1001</v>
       </c>
       <c r="S19">
         <v>2</v>
@@ -2311,17 +2331,20 @@
       <c r="L20">
         <v>2</v>
       </c>
-      <c r="M20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N20" t="s">
-        <v>48</v>
+      <c r="M20" s="2">
+        <v>10000017</v>
+      </c>
+      <c r="N20">
+        <v>10010017</v>
       </c>
       <c r="O20">
         <v>1</v>
       </c>
       <c r="P20">
         <v>10</v>
+      </c>
+      <c r="Q20">
+        <v>1001</v>
       </c>
       <c r="S20">
         <v>2</v>
@@ -2367,17 +2390,20 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" t="s">
-        <v>47</v>
-      </c>
-      <c r="N21" t="s">
-        <v>48</v>
+      <c r="M21" s="2">
+        <v>10000018</v>
+      </c>
+      <c r="N21">
+        <v>10010018</v>
       </c>
       <c r="O21">
         <v>1</v>
       </c>
       <c r="P21">
         <v>10</v>
+      </c>
+      <c r="Q21">
+        <v>1001</v>
       </c>
       <c r="S21">
         <v>2</v>
@@ -2423,17 +2449,20 @@
       <c r="L22">
         <v>2</v>
       </c>
-      <c r="M22" t="s">
-        <v>47</v>
-      </c>
-      <c r="N22" t="s">
-        <v>48</v>
+      <c r="M22" s="2">
+        <v>10000019</v>
+      </c>
+      <c r="N22">
+        <v>10010019</v>
       </c>
       <c r="O22">
         <v>1</v>
       </c>
       <c r="P22">
         <v>10</v>
+      </c>
+      <c r="Q22">
+        <v>1001</v>
       </c>
       <c r="S22">
         <v>2</v>
@@ -2479,17 +2508,20 @@
       <c r="L23">
         <v>2</v>
       </c>
-      <c r="M23" t="s">
-        <v>47</v>
-      </c>
-      <c r="N23" t="s">
-        <v>48</v>
+      <c r="M23" s="2">
+        <v>10000020</v>
+      </c>
+      <c r="N23">
+        <v>10010020</v>
       </c>
       <c r="O23">
         <v>1</v>
       </c>
       <c r="P23">
         <v>10</v>
+      </c>
+      <c r="Q23">
+        <v>1001</v>
       </c>
       <c r="S23">
         <v>2</v>
@@ -2535,17 +2567,20 @@
       <c r="L24">
         <v>2</v>
       </c>
-      <c r="M24" t="s">
-        <v>47</v>
-      </c>
-      <c r="N24" t="s">
-        <v>48</v>
+      <c r="M24" s="2">
+        <v>10000021</v>
+      </c>
+      <c r="N24">
+        <v>10010021</v>
       </c>
       <c r="O24">
         <v>1</v>
       </c>
       <c r="P24">
         <v>10</v>
+      </c>
+      <c r="Q24">
+        <v>1001</v>
       </c>
       <c r="S24">
         <v>2</v>
@@ -2591,17 +2626,20 @@
       <c r="L25">
         <v>2</v>
       </c>
-      <c r="M25" t="s">
-        <v>47</v>
-      </c>
-      <c r="N25" t="s">
-        <v>48</v>
+      <c r="M25" s="2">
+        <v>10000022</v>
+      </c>
+      <c r="N25">
+        <v>10010022</v>
       </c>
       <c r="O25">
         <v>1</v>
       </c>
       <c r="P25">
         <v>10</v>
+      </c>
+      <c r="Q25">
+        <v>1001</v>
       </c>
       <c r="S25">
         <v>2</v>
@@ -2647,17 +2685,20 @@
       <c r="L26">
         <v>2</v>
       </c>
-      <c r="M26" t="s">
-        <v>47</v>
-      </c>
-      <c r="N26" t="s">
-        <v>48</v>
+      <c r="M26" s="2">
+        <v>10000023</v>
+      </c>
+      <c r="N26">
+        <v>10010023</v>
       </c>
       <c r="O26">
         <v>1</v>
       </c>
       <c r="P26">
         <v>10</v>
+      </c>
+      <c r="Q26">
+        <v>1001</v>
       </c>
       <c r="S26">
         <v>2</v>
@@ -2703,17 +2744,20 @@
       <c r="L27">
         <v>2</v>
       </c>
-      <c r="M27" t="s">
-        <v>47</v>
-      </c>
-      <c r="N27" t="s">
-        <v>48</v>
+      <c r="M27" s="2">
+        <v>10000024</v>
+      </c>
+      <c r="N27">
+        <v>10010024</v>
       </c>
       <c r="O27">
         <v>1</v>
       </c>
       <c r="P27">
         <v>10</v>
+      </c>
+      <c r="Q27">
+        <v>1001</v>
       </c>
       <c r="S27">
         <v>2</v>
@@ -2759,17 +2803,20 @@
       <c r="L28">
         <v>2</v>
       </c>
-      <c r="M28" t="s">
-        <v>47</v>
-      </c>
-      <c r="N28" t="s">
-        <v>48</v>
+      <c r="M28" s="2">
+        <v>10000025</v>
+      </c>
+      <c r="N28">
+        <v>10010025</v>
       </c>
       <c r="O28">
         <v>1</v>
       </c>
       <c r="P28">
         <v>10</v>
+      </c>
+      <c r="Q28">
+        <v>1001</v>
       </c>
       <c r="S28">
         <v>2</v>
@@ -2815,17 +2862,20 @@
       <c r="L29">
         <v>2</v>
       </c>
-      <c r="M29" t="s">
-        <v>47</v>
-      </c>
-      <c r="N29" t="s">
-        <v>48</v>
+      <c r="M29" s="2">
+        <v>10000026</v>
+      </c>
+      <c r="N29">
+        <v>10010026</v>
       </c>
       <c r="O29">
         <v>1</v>
       </c>
       <c r="P29">
         <v>10</v>
+      </c>
+      <c r="Q29">
+        <v>1001</v>
       </c>
       <c r="S29">
         <v>2</v>
@@ -2871,17 +2921,20 @@
       <c r="L30">
         <v>2</v>
       </c>
-      <c r="M30" t="s">
-        <v>47</v>
-      </c>
-      <c r="N30" t="s">
-        <v>48</v>
+      <c r="M30" s="2">
+        <v>10000027</v>
+      </c>
+      <c r="N30">
+        <v>10010027</v>
       </c>
       <c r="O30">
         <v>1</v>
       </c>
       <c r="P30">
         <v>10</v>
+      </c>
+      <c r="Q30">
+        <v>1001</v>
       </c>
       <c r="S30">
         <v>2</v>
@@ -2927,17 +2980,20 @@
       <c r="L31">
         <v>2</v>
       </c>
-      <c r="M31" t="s">
-        <v>47</v>
-      </c>
-      <c r="N31" t="s">
-        <v>48</v>
+      <c r="M31" s="2">
+        <v>10000028</v>
+      </c>
+      <c r="N31">
+        <v>10010028</v>
       </c>
       <c r="O31">
         <v>1</v>
       </c>
       <c r="P31">
         <v>10</v>
+      </c>
+      <c r="Q31">
+        <v>1001</v>
       </c>
       <c r="S31">
         <v>2</v>
@@ -2983,17 +3039,20 @@
       <c r="L32">
         <v>2</v>
       </c>
-      <c r="M32" t="s">
-        <v>47</v>
-      </c>
-      <c r="N32" t="s">
-        <v>48</v>
+      <c r="M32" s="2">
+        <v>10000029</v>
+      </c>
+      <c r="N32">
+        <v>10010029</v>
       </c>
       <c r="O32">
         <v>1</v>
       </c>
       <c r="P32">
         <v>10</v>
+      </c>
+      <c r="Q32">
+        <v>1001</v>
       </c>
       <c r="S32">
         <v>2</v>
@@ -3039,17 +3098,20 @@
       <c r="L33">
         <v>2</v>
       </c>
-      <c r="M33" t="s">
-        <v>47</v>
-      </c>
-      <c r="N33" t="s">
-        <v>48</v>
+      <c r="M33" s="2">
+        <v>10000030</v>
+      </c>
+      <c r="N33">
+        <v>10010030</v>
       </c>
       <c r="O33">
         <v>1</v>
       </c>
       <c r="P33">
         <v>10</v>
+      </c>
+      <c r="Q33">
+        <v>1001</v>
       </c>
       <c r="S33">
         <v>2</v>
@@ -3095,17 +3157,20 @@
       <c r="L34">
         <v>2</v>
       </c>
-      <c r="M34" t="s">
-        <v>47</v>
-      </c>
-      <c r="N34" t="s">
-        <v>48</v>
+      <c r="M34" s="2">
+        <v>10000031</v>
+      </c>
+      <c r="N34">
+        <v>10010031</v>
       </c>
       <c r="O34">
         <v>1</v>
       </c>
       <c r="P34">
         <v>10</v>
+      </c>
+      <c r="Q34">
+        <v>1001</v>
       </c>
       <c r="S34">
         <v>2</v>
@@ -3151,17 +3216,20 @@
       <c r="L35">
         <v>2</v>
       </c>
-      <c r="M35" t="s">
-        <v>47</v>
-      </c>
-      <c r="N35" t="s">
-        <v>48</v>
+      <c r="M35" s="2">
+        <v>10000032</v>
+      </c>
+      <c r="N35">
+        <v>10010032</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35">
         <v>10</v>
+      </c>
+      <c r="Q35">
+        <v>1001</v>
       </c>
       <c r="S35">
         <v>2</v>
@@ -3207,17 +3275,20 @@
       <c r="L36">
         <v>2</v>
       </c>
-      <c r="M36" t="s">
-        <v>47</v>
-      </c>
-      <c r="N36" t="s">
-        <v>48</v>
+      <c r="M36" s="2">
+        <v>10000033</v>
+      </c>
+      <c r="N36">
+        <v>10010033</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36">
         <v>10</v>
+      </c>
+      <c r="Q36">
+        <v>1001</v>
       </c>
       <c r="S36">
         <v>2</v>
@@ -3263,17 +3334,20 @@
       <c r="L37">
         <v>2</v>
       </c>
-      <c r="M37" t="s">
-        <v>47</v>
-      </c>
-      <c r="N37" t="s">
-        <v>48</v>
+      <c r="M37" s="2">
+        <v>10000034</v>
+      </c>
+      <c r="N37">
+        <v>10010034</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37">
         <v>10</v>
+      </c>
+      <c r="Q37">
+        <v>1001</v>
       </c>
       <c r="S37">
         <v>2</v>
@@ -3319,17 +3393,20 @@
       <c r="L38">
         <v>2</v>
       </c>
-      <c r="M38" t="s">
-        <v>47</v>
-      </c>
-      <c r="N38" t="s">
-        <v>48</v>
+      <c r="M38" s="2">
+        <v>10000035</v>
+      </c>
+      <c r="N38">
+        <v>10010035</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
       <c r="P38">
         <v>10</v>
+      </c>
+      <c r="Q38">
+        <v>1001</v>
       </c>
       <c r="S38">
         <v>2</v>
@@ -3375,17 +3452,20 @@
       <c r="L39">
         <v>2</v>
       </c>
-      <c r="M39" t="s">
-        <v>47</v>
-      </c>
-      <c r="N39" t="s">
-        <v>48</v>
+      <c r="M39" s="2">
+        <v>10000036</v>
+      </c>
+      <c r="N39">
+        <v>10010036</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39">
         <v>10</v>
+      </c>
+      <c r="Q39">
+        <v>1001</v>
       </c>
       <c r="S39">
         <v>2</v>
@@ -3431,17 +3511,20 @@
       <c r="L40">
         <v>2</v>
       </c>
-      <c r="M40" t="s">
-        <v>47</v>
-      </c>
-      <c r="N40" t="s">
-        <v>48</v>
+      <c r="M40" s="2">
+        <v>10000037</v>
+      </c>
+      <c r="N40">
+        <v>10010037</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40">
         <v>10</v>
+      </c>
+      <c r="Q40">
+        <v>1001</v>
       </c>
       <c r="S40">
         <v>2</v>
@@ -3487,17 +3570,20 @@
       <c r="L41">
         <v>2</v>
       </c>
-      <c r="M41" t="s">
-        <v>47</v>
-      </c>
-      <c r="N41" t="s">
-        <v>48</v>
+      <c r="M41" s="2">
+        <v>10000038</v>
+      </c>
+      <c r="N41">
+        <v>10010038</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41">
         <v>10</v>
+      </c>
+      <c r="Q41">
+        <v>1001</v>
       </c>
       <c r="S41">
         <v>2</v>
@@ -3543,17 +3629,20 @@
       <c r="L42">
         <v>2</v>
       </c>
-      <c r="M42" t="s">
-        <v>47</v>
-      </c>
-      <c r="N42" t="s">
-        <v>48</v>
+      <c r="M42" s="2">
+        <v>10000039</v>
+      </c>
+      <c r="N42">
+        <v>10010039</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42">
         <v>10</v>
+      </c>
+      <c r="Q42">
+        <v>1001</v>
       </c>
       <c r="S42">
         <v>2</v>
@@ -3599,17 +3688,20 @@
       <c r="L43">
         <v>2</v>
       </c>
-      <c r="M43" t="s">
-        <v>47</v>
-      </c>
-      <c r="N43" t="s">
-        <v>48</v>
+      <c r="M43" s="2">
+        <v>10000040</v>
+      </c>
+      <c r="N43">
+        <v>10010040</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43">
         <v>10</v>
+      </c>
+      <c r="Q43">
+        <v>1001</v>
       </c>
       <c r="S43">
         <v>2</v>
@@ -3626,7 +3718,7 @@
         <v>100020001</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C44">
         <v>1000017</v>
@@ -3655,11 +3747,11 @@
       <c r="L44">
         <v>3</v>
       </c>
-      <c r="M44" t="s">
-        <v>50</v>
-      </c>
-      <c r="N44" t="s">
-        <v>48</v>
+      <c r="M44" s="2">
+        <v>10000041</v>
+      </c>
+      <c r="N44">
+        <v>10010041</v>
       </c>
       <c r="O44">
         <v>1</v>
@@ -3667,6 +3759,7 @@
       <c r="P44">
         <v>10</v>
       </c>
+      <c r="Q44"/>
       <c r="S44">
         <v>5</v>
       </c>
@@ -3676,7 +3769,7 @@
         <v>100030001</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>1000018</v>
@@ -3705,11 +3798,11 @@
       <c r="L45">
         <v>2</v>
       </c>
-      <c r="M45" t="s">
-        <v>52</v>
-      </c>
-      <c r="N45" t="s">
-        <v>48</v>
+      <c r="M45" s="2">
+        <v>10000042</v>
+      </c>
+      <c r="N45">
+        <v>10010042</v>
       </c>
       <c r="O45">
         <v>5</v>
@@ -3726,7 +3819,7 @@
         <v>100040001</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C46">
         <v>1000019</v>
@@ -3755,11 +3848,11 @@
       <c r="L46">
         <v>3</v>
       </c>
-      <c r="M46" t="s">
-        <v>54</v>
-      </c>
-      <c r="N46" t="s">
-        <v>48</v>
+      <c r="M46" s="2">
+        <v>10000043</v>
+      </c>
+      <c r="N46">
+        <v>10010043</v>
       </c>
       <c r="O46">
         <v>5</v>
@@ -3776,7 +3869,7 @@
         <v>100050001</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C47">
         <v>1000020</v>
@@ -3805,11 +3898,11 @@
       <c r="L47">
         <v>2</v>
       </c>
-      <c r="M47" t="s">
-        <v>56</v>
-      </c>
-      <c r="N47" t="s">
-        <v>48</v>
+      <c r="M47" s="2">
+        <v>10000044</v>
+      </c>
+      <c r="N47">
+        <v>10010044</v>
       </c>
       <c r="O47">
         <v>2</v>
@@ -3826,7 +3919,7 @@
         <v>100060001</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C48">
         <v>1000021</v>
@@ -3855,11 +3948,11 @@
       <c r="L48">
         <v>3</v>
       </c>
-      <c r="M48" t="s">
-        <v>58</v>
-      </c>
-      <c r="N48" t="s">
-        <v>48</v>
+      <c r="M48" s="2">
+        <v>10000045</v>
+      </c>
+      <c r="N48">
+        <v>10010045</v>
       </c>
       <c r="O48">
         <v>2</v>
@@ -3876,7 +3969,7 @@
         <v>100070001</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>1000022</v>
@@ -3902,11 +3995,11 @@
       <c r="L49">
         <v>2</v>
       </c>
-      <c r="M49" t="s">
-        <v>60</v>
-      </c>
-      <c r="N49" t="s">
-        <v>48</v>
+      <c r="M49" s="2">
+        <v>10000046</v>
+      </c>
+      <c r="N49">
+        <v>10010046</v>
       </c>
       <c r="O49">
         <v>1</v>
@@ -3923,7 +4016,7 @@
         <v>100080001</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C50">
         <v>1000023</v>
@@ -3949,11 +4042,11 @@
       <c r="L50">
         <v>3</v>
       </c>
-      <c r="M50" t="s">
-        <v>62</v>
-      </c>
-      <c r="N50" t="s">
-        <v>48</v>
+      <c r="M50" s="2">
+        <v>10000047</v>
+      </c>
+      <c r="N50">
+        <v>10010047</v>
       </c>
       <c r="O50">
         <v>1</v>
@@ -3970,7 +4063,7 @@
         <v>100090001</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C51">
         <v>1000024</v>
@@ -3996,11 +4089,11 @@
       <c r="L51">
         <v>2</v>
       </c>
-      <c r="M51" t="s">
-        <v>64</v>
-      </c>
-      <c r="N51" t="s">
-        <v>48</v>
+      <c r="M51" s="2">
+        <v>10000048</v>
+      </c>
+      <c r="N51">
+        <v>10010048</v>
       </c>
       <c r="O51">
         <v>3</v>
@@ -4017,7 +4110,7 @@
         <v>100100001</v>
       </c>
       <c r="B52" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C52">
         <v>1000025</v>
@@ -4043,11 +4136,11 @@
       <c r="L52">
         <v>3</v>
       </c>
-      <c r="M52" t="s">
-        <v>66</v>
-      </c>
-      <c r="N52" t="s">
-        <v>48</v>
+      <c r="M52" s="2">
+        <v>10000049</v>
+      </c>
+      <c r="N52">
+        <v>10010049</v>
       </c>
       <c r="O52">
         <v>3</v>
@@ -4093,11 +4186,11 @@
       <c r="L53">
         <v>2</v>
       </c>
-      <c r="M53" t="s">
-        <v>47</v>
-      </c>
-      <c r="N53" t="s">
-        <v>48</v>
+      <c r="M53" s="2">
+        <v>10000050</v>
+      </c>
+      <c r="N53">
+        <v>10010050</v>
       </c>
       <c r="O53">
         <v>1</v>
@@ -4114,7 +4207,7 @@
         <v>200020001</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C54">
         <v>1000017</v>
@@ -4143,11 +4236,11 @@
       <c r="L54">
         <v>3</v>
       </c>
-      <c r="M54" t="s">
-        <v>50</v>
-      </c>
-      <c r="N54" t="s">
-        <v>48</v>
+      <c r="M54" s="2">
+        <v>10000051</v>
+      </c>
+      <c r="N54">
+        <v>10010051</v>
       </c>
       <c r="O54">
         <v>1</v>
@@ -4164,7 +4257,7 @@
         <v>200030001</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C55">
         <v>1000018</v>
@@ -4193,11 +4286,11 @@
       <c r="L55">
         <v>2</v>
       </c>
-      <c r="M55" t="s">
-        <v>52</v>
-      </c>
-      <c r="N55" t="s">
-        <v>48</v>
+      <c r="M55" s="2">
+        <v>10000052</v>
+      </c>
+      <c r="N55">
+        <v>10010052</v>
       </c>
       <c r="O55">
         <v>5</v>
@@ -4214,7 +4307,7 @@
         <v>200040001</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C56">
         <v>1000019</v>
@@ -4243,11 +4336,11 @@
       <c r="L56">
         <v>3</v>
       </c>
-      <c r="M56" t="s">
-        <v>54</v>
-      </c>
-      <c r="N56" t="s">
-        <v>48</v>
+      <c r="M56" s="2">
+        <v>10000053</v>
+      </c>
+      <c r="N56">
+        <v>10010053</v>
       </c>
       <c r="O56">
         <v>5</v>
@@ -4264,7 +4357,7 @@
         <v>200050001</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C57">
         <v>1000020</v>
@@ -4293,11 +4386,11 @@
       <c r="L57">
         <v>2</v>
       </c>
-      <c r="M57" t="s">
-        <v>56</v>
-      </c>
-      <c r="N57" t="s">
-        <v>48</v>
+      <c r="M57" s="2">
+        <v>10000054</v>
+      </c>
+      <c r="N57">
+        <v>10010054</v>
       </c>
       <c r="O57">
         <v>2</v>
@@ -4314,7 +4407,7 @@
         <v>200060001</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C58">
         <v>1000021</v>
@@ -4343,11 +4436,11 @@
       <c r="L58">
         <v>3</v>
       </c>
-      <c r="M58" t="s">
-        <v>58</v>
-      </c>
-      <c r="N58" t="s">
-        <v>48</v>
+      <c r="M58" s="2">
+        <v>10000055</v>
+      </c>
+      <c r="N58">
+        <v>10010055</v>
       </c>
       <c r="O58">
         <v>2</v>
@@ -4364,7 +4457,7 @@
         <v>200070001</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C59">
         <v>1000022</v>
@@ -4390,11 +4483,11 @@
       <c r="L59">
         <v>2</v>
       </c>
-      <c r="M59" t="s">
-        <v>60</v>
-      </c>
-      <c r="N59" t="s">
-        <v>48</v>
+      <c r="M59" s="2">
+        <v>10000056</v>
+      </c>
+      <c r="N59">
+        <v>10010056</v>
       </c>
       <c r="O59">
         <v>1</v>
@@ -4411,7 +4504,7 @@
         <v>200080001</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C60">
         <v>1000023</v>
@@ -4437,11 +4530,11 @@
       <c r="L60">
         <v>3</v>
       </c>
-      <c r="M60" t="s">
-        <v>62</v>
-      </c>
-      <c r="N60" t="s">
-        <v>48</v>
+      <c r="M60" s="2">
+        <v>10000057</v>
+      </c>
+      <c r="N60">
+        <v>10010057</v>
       </c>
       <c r="O60">
         <v>1</v>
@@ -4458,7 +4551,7 @@
         <v>200090001</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C61">
         <v>1000024</v>
@@ -4484,11 +4577,11 @@
       <c r="L61">
         <v>2</v>
       </c>
-      <c r="M61" t="s">
-        <v>64</v>
-      </c>
-      <c r="N61" t="s">
-        <v>48</v>
+      <c r="M61" s="2">
+        <v>10000058</v>
+      </c>
+      <c r="N61">
+        <v>10010058</v>
       </c>
       <c r="O61">
         <v>3</v>
@@ -4505,7 +4598,7 @@
         <v>200100001</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C62">
         <v>1000025</v>
@@ -4531,11 +4624,11 @@
       <c r="L62">
         <v>3</v>
       </c>
-      <c r="M62" t="s">
-        <v>66</v>
-      </c>
-      <c r="N62" t="s">
-        <v>48</v>
+      <c r="M62" s="2">
+        <v>10000059</v>
+      </c>
+      <c r="N62">
+        <v>10010059</v>
       </c>
       <c r="O62">
         <v>3</v>
